--- a/hall/resources/sample/EmployeeProfile.xlsx
+++ b/hall/resources/sample/EmployeeProfile.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="EmployeeProfile" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -58,8 +59,86 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="E13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1026代表雇员类别-导玩员（游戏区）</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1027代表雇员类别-服务员员（休息区）
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E23" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1028代表雇员类别-管理员（管理区）
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="58">
   <si>
     <t>雇员ID</t>
   </si>
@@ -67,6 +146,9 @@
     <t>序列ID</t>
   </si>
   <si>
+    <t>道具ID_碎片ID_碎片数量</t>
+  </si>
+  <si>
     <t>名称</t>
   </si>
   <si>
@@ -79,25 +161,40 @@
     <t>雇员品质</t>
   </si>
   <si>
+    <t>技能</t>
+  </si>
+  <si>
     <t>品质名称备注</t>
   </si>
   <si>
     <t>int</t>
   </si>
   <si>
+    <t>list&lt;int&gt;{_}</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
     <t>SequenceID</t>
   </si>
   <si>
+    <t>DuplicatetoShard</t>
+  </si>
+  <si>
     <t>ProfessionID</t>
   </si>
   <si>
     <t>EmployeeQuality</t>
   </si>
   <si>
-    <t>张三</t>
+    <t>SkillIdList</t>
+  </si>
+  <si>
+    <t>1026001_1126001_2</t>
+  </si>
+  <si>
+    <t>威廉</t>
   </si>
   <si>
     <t>导玩员</t>
@@ -106,64 +203,115 @@
     <t>初级</t>
   </si>
   <si>
-    <t>张四</t>
+    <t>1026101_1126101_4</t>
+  </si>
+  <si>
+    <t>亨利</t>
   </si>
   <si>
     <t>中级</t>
   </si>
   <si>
-    <t>张五</t>
+    <t>1026201_1126201_6</t>
+  </si>
+  <si>
+    <t>乔治</t>
   </si>
   <si>
     <t>高级</t>
   </si>
   <si>
-    <t>张武</t>
+    <t>1026301_1126301_8</t>
+  </si>
+  <si>
+    <t>亚瑟</t>
   </si>
   <si>
     <t>金牌</t>
   </si>
   <si>
-    <t>账务</t>
+    <t>1026401_1126401_10</t>
+  </si>
+  <si>
+    <t>马修</t>
   </si>
   <si>
     <t>王牌</t>
   </si>
   <si>
-    <t>王二</t>
+    <t>1027001_1127001_2</t>
+  </si>
+  <si>
+    <t>拉斐尔</t>
   </si>
   <si>
     <t>服务员</t>
   </si>
   <si>
-    <t>王三</t>
-  </si>
-  <si>
-    <t>王四</t>
-  </si>
-  <si>
-    <t>王五</t>
-  </si>
-  <si>
-    <t>王六</t>
-  </si>
-  <si>
-    <t>李三</t>
+    <t>1027101_1127101_4</t>
+  </si>
+  <si>
+    <t>埃米尔</t>
+  </si>
+  <si>
+    <t>1027201_1127201_6</t>
+  </si>
+  <si>
+    <t>雷蒙德</t>
+  </si>
+  <si>
+    <t>1027301_1127301_8</t>
+  </si>
+  <si>
+    <t>丹尼尔</t>
+  </si>
+  <si>
+    <t>1027401_1127401_10</t>
+  </si>
+  <si>
+    <t>卢卡斯</t>
+  </si>
+  <si>
+    <t>1028001_1128001_2</t>
+  </si>
+  <si>
+    <t>尼古拉斯</t>
   </si>
   <si>
     <t>管理员</t>
   </si>
   <si>
-    <t>李四</t>
-  </si>
-  <si>
-    <t>李二</t>
-  </si>
-  <si>
-    <t>李毅</t>
-  </si>
-  <si>
-    <t>李武</t>
+    <t>1028101_1128101_4</t>
+  </si>
+  <si>
+    <t>亚历山大</t>
+  </si>
+  <si>
+    <t>1028201_1128201_6</t>
+  </si>
+  <si>
+    <t>奥古斯特</t>
+  </si>
+  <si>
+    <t>1028301_1128301_8</t>
+  </si>
+  <si>
+    <t>费利克斯</t>
+  </si>
+  <si>
+    <t>1028401_1128401_10</t>
+  </si>
+  <si>
+    <t>阿尔弗雷德</t>
+  </si>
+  <si>
+    <t>道具ID</t>
+  </si>
+  <si>
+    <t>碎片ID</t>
+  </si>
+  <si>
+    <t>分解数量</t>
   </si>
 </sst>
 </file>
@@ -176,13 +324,25 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF212529"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -340,12 +500,18 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -687,150 +853,174 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1358,442 +1548,803 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:I19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.75" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="21.75" style="1" customWidth="1"/>
+    <col min="1" max="1" width="11.75" style="4" customWidth="1"/>
+    <col min="2" max="2" width="13.875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="21.375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="14" style="4" customWidth="1"/>
+    <col min="5" max="5" width="14.375" style="4" customWidth="1"/>
+    <col min="6" max="6" width="14.875" style="4" customWidth="1"/>
+    <col min="7" max="7" width="16.875" style="4" customWidth="1"/>
+    <col min="8" max="8" width="21.25" style="5" customWidth="1"/>
+    <col min="9" max="9" width="21.75" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:9">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="2" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="I1" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="6"/>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="6"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="6"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="6">
+        <f>E5*10000+G5*1000+B5</f>
+        <v>101001</v>
+      </c>
+      <c r="B5" s="11">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="11">
+        <v>10</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="11">
+        <v>1</v>
+      </c>
+      <c r="H5" s="10">
+        <v>100101</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="6">
+        <f t="shared" ref="A6:A19" si="0">E6*10000+G6*1000+B6</f>
+        <v>102002</v>
+      </c>
+      <c r="B6" s="11">
+        <v>2</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="11">
+        <v>10</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="11">
+        <v>2</v>
+      </c>
+      <c r="H6" s="10">
+        <v>100102</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="6">
+        <f t="shared" si="0"/>
+        <v>103003</v>
+      </c>
+      <c r="B7" s="11">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="11">
+        <v>10</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="11">
+        <v>3</v>
+      </c>
+      <c r="H7" s="10">
+        <v>100103</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="6">
+        <f t="shared" si="0"/>
+        <v>104004</v>
+      </c>
+      <c r="B8" s="11">
+        <v>4</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="11">
+        <v>10</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" s="11">
+        <v>4</v>
+      </c>
+      <c r="H8" s="10">
+        <v>100201</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="6">
+        <f t="shared" si="0"/>
+        <v>105005</v>
+      </c>
+      <c r="B9" s="11">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="11">
+        <v>10</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="11">
+        <v>5</v>
+      </c>
+      <c r="H9" s="10">
+        <v>100202</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="6">
+        <f t="shared" si="0"/>
+        <v>201006</v>
+      </c>
+      <c r="B10" s="11">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="6">
+        <v>20</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="12">
+        <v>1</v>
+      </c>
+      <c r="H10" s="10">
+        <v>200101</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="6">
+        <f t="shared" si="0"/>
+        <v>202007</v>
+      </c>
+      <c r="B11" s="11">
         <v>7</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="2" t="s">
+      <c r="C11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="6">
+        <v>20</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" s="12">
+        <v>2</v>
+      </c>
+      <c r="H11" s="10">
+        <v>200102</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="6">
+        <f t="shared" si="0"/>
+        <v>203008</v>
+      </c>
+      <c r="B12" s="11">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="6">
+        <v>20</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="12">
+        <v>3</v>
+      </c>
+      <c r="H12" s="10">
+        <v>200103</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="6">
+        <f t="shared" si="0"/>
+        <v>204009</v>
+      </c>
+      <c r="B13" s="11">
         <v>9</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="s">
+      <c r="C13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="6">
+        <v>20</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" s="12">
+        <v>4</v>
+      </c>
+      <c r="H13" s="10">
+        <v>200201</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="6">
+        <f t="shared" si="0"/>
+        <v>205010</v>
+      </c>
+      <c r="B14" s="11">
         <v>10</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2" t="s">
+      <c r="C14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="6">
+        <v>20</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" s="12">
+        <v>5</v>
+      </c>
+      <c r="H14" s="10">
+        <v>200202</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="6">
+        <f t="shared" si="0"/>
+        <v>301011</v>
+      </c>
+      <c r="B15" s="11">
         <v>11</v>
       </c>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="2">
-        <f>D5*10000+F5*1000+B5</f>
-        <v>101001</v>
-      </c>
-      <c r="B5" s="3">
+      <c r="C15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" s="6">
+        <v>30</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G15" s="6">
         <v>1</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="H15" s="10">
+        <v>300101</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="6">
+        <f t="shared" si="0"/>
+        <v>302012</v>
+      </c>
+      <c r="B16" s="11">
         <v>12</v>
       </c>
-      <c r="D5" s="3">
+      <c r="C16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="6">
+        <v>30</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G16" s="6">
+        <v>2</v>
+      </c>
+      <c r="H16" s="10">
+        <v>300102</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="6">
+        <f t="shared" si="0"/>
+        <v>303013</v>
+      </c>
+      <c r="B17" s="11">
+        <v>13</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17" s="6">
+        <v>30</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="6">
+        <v>3</v>
+      </c>
+      <c r="H17" s="10">
+        <v>300103</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="6">
+        <f t="shared" si="0"/>
+        <v>304014</v>
+      </c>
+      <c r="B18" s="11">
+        <v>14</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="6">
+        <v>30</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G18" s="6">
+        <v>4</v>
+      </c>
+      <c r="H18" s="10">
+        <v>300201</v>
+      </c>
+      <c r="I18" s="12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="6">
+        <f t="shared" si="0"/>
+        <v>305015</v>
+      </c>
+      <c r="B19" s="11">
+        <v>15</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19" s="6">
+        <v>30</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G19" s="6">
+        <v>5</v>
+      </c>
+      <c r="H19" s="10">
+        <v>300202</v>
+      </c>
+      <c r="I19" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="D11:H27"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <sheetData>
+    <row r="11" spans="4:8">
+      <c r="D11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="4:8">
+      <c r="D13" s="1">
+        <v>1026001</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1126001</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="H13" s="3" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,D13,E13,F13)</f>
+        <v>1026001_1126001_2</v>
+      </c>
+    </row>
+    <row r="14" spans="4:8">
+      <c r="D14" s="1">
+        <v>1026101</v>
+      </c>
+      <c r="E14" s="2">
+        <v>1126101</v>
+      </c>
+      <c r="F14">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3" t="str">
+        <f t="shared" ref="H14:H27" si="0">_xlfn.TEXTJOIN("_",TRUE,D14,E14,F14)</f>
+        <v>1026101_1126101_4</v>
+      </c>
+    </row>
+    <row r="15" spans="4:8">
+      <c r="D15" s="1">
+        <v>1026201</v>
+      </c>
+      <c r="E15" s="2">
+        <v>1126201</v>
+      </c>
+      <c r="F15">
+        <v>6</v>
+      </c>
+      <c r="H15" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>1026201_1126201_6</v>
+      </c>
+    </row>
+    <row r="16" spans="4:8">
+      <c r="D16" s="1">
+        <v>1026301</v>
+      </c>
+      <c r="E16" s="2">
+        <v>1126301</v>
+      </c>
+      <c r="F16">
+        <v>8</v>
+      </c>
+      <c r="H16" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>1026301_1126301_8</v>
+      </c>
+    </row>
+    <row r="17" spans="4:8">
+      <c r="D17" s="1">
+        <v>1026401</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1126401</v>
+      </c>
+      <c r="F17">
         <v>10</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="3">
-        <v>1</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="2">
-        <f t="shared" ref="A6:A19" si="0">D6*10000+F6*1000+B6</f>
-        <v>102002</v>
-      </c>
-      <c r="B6" s="3">
+      <c r="H17" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>1026401_1126401_10</v>
+      </c>
+    </row>
+    <row r="18" spans="4:8">
+      <c r="D18" s="1">
+        <v>1027001</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1127001</v>
+      </c>
+      <c r="F18">
         <v>2</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="3">
+      <c r="H18" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>1027001_1127001_2</v>
+      </c>
+    </row>
+    <row r="19" spans="4:8">
+      <c r="D19" s="1">
+        <v>1027101</v>
+      </c>
+      <c r="E19" s="2">
+        <v>1127101</v>
+      </c>
+      <c r="F19">
+        <v>4</v>
+      </c>
+      <c r="H19" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>1027101_1127101_4</v>
+      </c>
+    </row>
+    <row r="20" spans="4:8">
+      <c r="D20" s="1">
+        <v>1027201</v>
+      </c>
+      <c r="E20" s="2">
+        <v>1127201</v>
+      </c>
+      <c r="F20">
+        <v>6</v>
+      </c>
+      <c r="H20" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>1027201_1127201_6</v>
+      </c>
+    </row>
+    <row r="21" spans="4:8">
+      <c r="D21" s="1">
+        <v>1027301</v>
+      </c>
+      <c r="E21" s="2">
+        <v>1127301</v>
+      </c>
+      <c r="F21">
+        <v>8</v>
+      </c>
+      <c r="H21" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>1027301_1127301_8</v>
+      </c>
+    </row>
+    <row r="22" spans="4:8">
+      <c r="D22" s="1">
+        <v>1027401</v>
+      </c>
+      <c r="E22" s="2">
+        <v>1127401</v>
+      </c>
+      <c r="F22">
         <v>10</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="3">
+      <c r="H22" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>1027401_1127401_10</v>
+      </c>
+    </row>
+    <row r="23" spans="4:8">
+      <c r="D23" s="1">
+        <v>1028001</v>
+      </c>
+      <c r="E23" s="2">
+        <v>1128001</v>
+      </c>
+      <c r="F23">
         <v>2</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="2">
-        <f t="shared" si="0"/>
-        <v>103003</v>
-      </c>
-      <c r="B7" s="3">
-        <v>3</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="3">
+      <c r="H23" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>1028001_1128001_2</v>
+      </c>
+    </row>
+    <row r="24" spans="4:8">
+      <c r="D24" s="1">
+        <v>1028101</v>
+      </c>
+      <c r="E24" s="2">
+        <v>1128101</v>
+      </c>
+      <c r="F24">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>1028101_1128101_4</v>
+      </c>
+    </row>
+    <row r="25" spans="4:8">
+      <c r="D25" s="1">
+        <v>1028201</v>
+      </c>
+      <c r="E25" s="2">
+        <v>1128201</v>
+      </c>
+      <c r="F25">
+        <v>6</v>
+      </c>
+      <c r="H25" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>1028201_1128201_6</v>
+      </c>
+    </row>
+    <row r="26" spans="4:8">
+      <c r="D26" s="1">
+        <v>1028301</v>
+      </c>
+      <c r="E26" s="2">
+        <v>1128301</v>
+      </c>
+      <c r="F26">
+        <v>8</v>
+      </c>
+      <c r="H26" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>1028301_1128301_8</v>
+      </c>
+    </row>
+    <row r="27" spans="4:8">
+      <c r="D27" s="1">
+        <v>1028401</v>
+      </c>
+      <c r="E27" s="2">
+        <v>1128401</v>
+      </c>
+      <c r="F27">
         <v>10</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="3">
-        <v>3</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="2">
-        <f t="shared" si="0"/>
-        <v>104004</v>
-      </c>
-      <c r="B8" s="3">
-        <v>4</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="3">
-        <v>10</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="3">
-        <v>4</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="2">
-        <f t="shared" si="0"/>
-        <v>105005</v>
-      </c>
-      <c r="B9" s="3">
-        <v>5</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="3">
-        <v>10</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="3">
-        <v>5</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="2">
-        <f t="shared" si="0"/>
-        <v>201006</v>
-      </c>
-      <c r="B10" s="3">
-        <v>6</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="2">
-        <v>20</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" s="4">
-        <v>1</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="2">
-        <f t="shared" si="0"/>
-        <v>202007</v>
-      </c>
-      <c r="B11" s="3">
-        <v>7</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="2">
-        <v>20</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="4">
-        <v>2</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="2">
-        <f t="shared" si="0"/>
-        <v>203008</v>
-      </c>
-      <c r="B12" s="3">
-        <v>8</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="2">
-        <v>20</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F12" s="4">
-        <v>3</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="2">
-        <f t="shared" si="0"/>
-        <v>204009</v>
-      </c>
-      <c r="B13" s="3">
-        <v>9</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="2">
-        <v>20</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F13" s="4">
-        <v>4</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="2">
-        <f t="shared" si="0"/>
-        <v>205010</v>
-      </c>
-      <c r="B14" s="3">
-        <v>10</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" s="2">
-        <v>20</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" s="4">
-        <v>5</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="2">
-        <f t="shared" si="0"/>
-        <v>301011</v>
-      </c>
-      <c r="B15" s="3">
-        <v>11</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" s="2">
-        <v>30</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F15" s="2">
-        <v>1</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="2">
-        <f t="shared" si="0"/>
-        <v>302012</v>
-      </c>
-      <c r="B16" s="3">
-        <v>12</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D16" s="2">
-        <v>30</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F16" s="2">
-        <v>2</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="2">
-        <f t="shared" si="0"/>
-        <v>303013</v>
-      </c>
-      <c r="B17" s="3">
-        <v>13</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" s="2">
-        <v>30</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F17" s="2">
-        <v>3</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="2">
-        <f t="shared" si="0"/>
-        <v>304014</v>
-      </c>
-      <c r="B18" s="3">
-        <v>14</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18" s="2">
-        <v>30</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F18" s="2">
-        <v>4</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="2">
-        <f t="shared" si="0"/>
-        <v>305015</v>
-      </c>
-      <c r="B19" s="3">
-        <v>15</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19" s="2">
-        <v>30</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F19" s="2">
-        <v>5</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>22</v>
+      <c r="H27" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>1028401_1128401_10</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/EmployeeProfile.xlsx
+++ b/hall/resources/sample/EmployeeProfile.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="EmployeeProfile" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -138,7 +138,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="60">
   <si>
     <t>雇员ID</t>
   </si>
@@ -149,6 +149,9 @@
     <t>道具ID_碎片ID_碎片数量</t>
   </si>
   <si>
+    <t>雇员名称</t>
+  </si>
+  <si>
     <t>名称</t>
   </si>
   <si>
@@ -180,6 +183,9 @@
   </si>
   <si>
     <t>DuplicatetoShard</t>
+  </si>
+  <si>
+    <t>NameId</t>
   </si>
   <si>
     <t>ProfessionID</t>
@@ -1548,21 +1554,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.75" style="4" customWidth="1"/>
     <col min="2" max="2" width="13.875" style="4" customWidth="1"/>
     <col min="3" max="3" width="21.375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="14" style="4" customWidth="1"/>
-    <col min="5" max="5" width="14.375" style="4" customWidth="1"/>
-    <col min="6" max="6" width="14.875" style="4" customWidth="1"/>
-    <col min="7" max="7" width="16.875" style="4" customWidth="1"/>
-    <col min="8" max="8" width="21.25" style="5" customWidth="1"/>
-    <col min="9" max="9" width="21.75" style="4" customWidth="1"/>
+    <col min="4" max="4" width="8.375" style="4" customWidth="1"/>
+    <col min="5" max="5" width="14" style="4" customWidth="1"/>
+    <col min="6" max="6" width="14.375" style="4" customWidth="1"/>
+    <col min="7" max="7" width="14.875" style="4" customWidth="1"/>
+    <col min="8" max="8" width="16.875" style="4" customWidth="1"/>
+    <col min="9" max="9" width="21.25" style="5" customWidth="1"/>
+    <col min="10" max="10" width="21.75" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1572,7 +1579,7 @@
       <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="6" t="s">
@@ -1584,60 +1591,69 @@
       <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="9" t="s">
+      <c r="E2" s="6"/>
+      <c r="F2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="6"/>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="G2" s="6"/>
+      <c r="H2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="6"/>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="E3" s="6"/>
+      <c r="F3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="6"/>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="G3" s="6"/>
+      <c r="H3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="6"/>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1645,70 +1661,77 @@
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="6"/>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="H4" s="6"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="6"/>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="6">
-        <f>E5*10000+G5*1000+B5</f>
+        <f>F5*10000+H5*1000+B5</f>
         <v>101001</v>
       </c>
       <c r="B5" s="11">
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="11">
+        <v>19</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1026001</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="11">
         <v>10</v>
       </c>
-      <c r="F5" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="11">
+      <c r="G5" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="11">
         <v>1</v>
       </c>
-      <c r="H5" s="10">
+      <c r="I5" s="10">
         <v>100101</v>
       </c>
-      <c r="I5" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="J5" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="6">
-        <f t="shared" ref="A6:A19" si="0">E6*10000+G6*1000+B6</f>
+        <f t="shared" ref="A6:A19" si="0">F6*10000+H6*1000+B6</f>
         <v>102002</v>
       </c>
       <c r="B6" s="11">
         <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1026002</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="11">
+        <v>10</v>
+      </c>
+      <c r="G6" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="11">
-        <v>10</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" s="11">
+      <c r="H6" s="11">
         <v>2</v>
       </c>
-      <c r="H6" s="10">
+      <c r="I6" s="10">
         <v>100102</v>
       </c>
-      <c r="I6" s="11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="J6" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="6">
         <f t="shared" si="0"/>
         <v>103003</v>
@@ -1717,28 +1740,31 @@
         <v>3</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="11">
+        <v>26</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1026101</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="11">
         <v>10</v>
       </c>
-      <c r="F7" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="11">
+      <c r="G7" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="11">
         <v>3</v>
       </c>
-      <c r="H7" s="10">
+      <c r="I7" s="10">
         <v>100103</v>
       </c>
-      <c r="I7" s="11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="J7" s="11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="6">
         <f t="shared" si="0"/>
         <v>104004</v>
@@ -1747,28 +1773,31 @@
         <v>4</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="11">
+        <v>29</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1026102</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="11">
         <v>10</v>
       </c>
-      <c r="F8" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" s="11">
+      <c r="G8" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="11">
         <v>4</v>
       </c>
-      <c r="H8" s="10">
+      <c r="I8" s="10">
         <v>100201</v>
       </c>
-      <c r="I8" s="12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="J8" s="12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="6">
         <f t="shared" si="0"/>
         <v>105005</v>
@@ -1777,28 +1806,31 @@
         <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="11">
+        <v>32</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1026201</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="11">
         <v>10</v>
       </c>
-      <c r="F9" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" s="11">
+      <c r="G9" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="11">
         <v>5</v>
       </c>
-      <c r="H9" s="10">
+      <c r="I9" s="10">
         <v>100202</v>
       </c>
-      <c r="I9" s="12" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="J9" s="12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" s="6">
         <f t="shared" si="0"/>
         <v>201006</v>
@@ -1807,28 +1839,31 @@
         <v>6</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="6">
+        <v>35</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1026202</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="6">
         <v>20</v>
       </c>
-      <c r="F10" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10" s="12">
+      <c r="G10" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" s="12">
         <v>1</v>
       </c>
-      <c r="H10" s="10">
+      <c r="I10" s="10">
         <v>200101</v>
       </c>
-      <c r="I10" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="J10" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" s="6">
         <f t="shared" si="0"/>
         <v>202007</v>
@@ -1837,28 +1872,31 @@
         <v>7</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1026301</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" s="6">
+        <v>20</v>
+      </c>
+      <c r="G11" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="6">
-        <v>20</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G11" s="12">
+      <c r="H11" s="12">
         <v>2</v>
       </c>
-      <c r="H11" s="10">
+      <c r="I11" s="10">
         <v>200102</v>
       </c>
-      <c r="I11" s="11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="J11" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" s="6">
         <f t="shared" si="0"/>
         <v>203008</v>
@@ -1867,28 +1905,31 @@
         <v>8</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E12" s="6">
+        <v>40</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1026302</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" s="6">
         <v>20</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G12" s="12">
+      <c r="G12" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H12" s="12">
         <v>3</v>
       </c>
-      <c r="H12" s="10">
+      <c r="I12" s="10">
         <v>200103</v>
       </c>
-      <c r="I12" s="11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
+      <c r="J12" s="11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" s="6">
         <f t="shared" si="0"/>
         <v>204009</v>
@@ -1897,28 +1938,31 @@
         <v>9</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E13" s="6">
+        <v>42</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1026401</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" s="6">
         <v>20</v>
       </c>
-      <c r="F13" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G13" s="12">
+      <c r="G13" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" s="12">
         <v>4</v>
       </c>
-      <c r="H13" s="10">
+      <c r="I13" s="10">
         <v>200201</v>
       </c>
-      <c r="I13" s="12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+      <c r="J13" s="12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" s="6">
         <f t="shared" si="0"/>
         <v>205010</v>
@@ -1927,28 +1971,31 @@
         <v>10</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="6">
+        <v>44</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1026402</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14" s="6">
         <v>20</v>
       </c>
-      <c r="F14" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G14" s="12">
+      <c r="G14" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14" s="12">
         <v>5</v>
       </c>
-      <c r="H14" s="10">
+      <c r="I14" s="10">
         <v>200202</v>
       </c>
-      <c r="I14" s="12" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
+      <c r="J14" s="12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" s="6">
         <f t="shared" si="0"/>
         <v>301011</v>
@@ -1957,28 +2004,31 @@
         <v>11</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E15" s="6">
+        <v>46</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1027001</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" s="6">
         <v>30</v>
       </c>
-      <c r="F15" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G15" s="6">
+      <c r="G15" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H15" s="6">
         <v>1</v>
       </c>
-      <c r="H15" s="10">
+      <c r="I15" s="10">
         <v>300101</v>
       </c>
-      <c r="I15" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
+      <c r="J15" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" s="6">
         <f t="shared" si="0"/>
         <v>302012</v>
@@ -1987,28 +2037,31 @@
         <v>12</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1027002</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F16" s="6">
+        <v>30</v>
+      </c>
+      <c r="G16" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E16" s="6">
-        <v>30</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G16" s="6">
+      <c r="H16" s="6">
         <v>2</v>
       </c>
-      <c r="H16" s="10">
+      <c r="I16" s="10">
         <v>300102</v>
       </c>
-      <c r="I16" s="11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
+      <c r="J16" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" s="6">
         <f t="shared" si="0"/>
         <v>303013</v>
@@ -2017,28 +2070,31 @@
         <v>13</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E17" s="6">
+        <v>51</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1027101</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F17" s="6">
         <v>30</v>
       </c>
-      <c r="F17" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G17" s="6">
+      <c r="G17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H17" s="6">
         <v>3</v>
       </c>
-      <c r="H17" s="10">
+      <c r="I17" s="10">
         <v>300103</v>
       </c>
-      <c r="I17" s="11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
+      <c r="J17" s="11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="6">
         <f t="shared" si="0"/>
         <v>304014</v>
@@ -2047,28 +2103,31 @@
         <v>14</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" s="6">
+        <v>53</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1027102</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18" s="6">
         <v>30</v>
       </c>
-      <c r="F18" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G18" s="6">
+      <c r="G18" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H18" s="6">
         <v>4</v>
       </c>
-      <c r="H18" s="10">
+      <c r="I18" s="10">
         <v>300201</v>
       </c>
-      <c r="I18" s="12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
+      <c r="J18" s="12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" s="6">
         <f t="shared" si="0"/>
         <v>305015</v>
@@ -2077,25 +2136,28 @@
         <v>15</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E19" s="6">
+        <v>55</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1027201</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F19" s="6">
         <v>30</v>
       </c>
-      <c r="F19" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G19" s="6">
+      <c r="G19" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H19" s="6">
         <v>5</v>
       </c>
-      <c r="H19" s="10">
+      <c r="I19" s="10">
         <v>300202</v>
       </c>
-      <c r="I19" s="12" t="s">
-        <v>32</v>
+      <c r="J19" s="12" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -2113,13 +2175,13 @@
   <sheetData>
     <row r="11" spans="4:8">
       <c r="D11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E11" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="4:8">

--- a/hall/resources/sample/EmployeeProfile.xlsx
+++ b/hall/resources/sample/EmployeeProfile.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="EmployeeProfile" sheetId="1" r:id="rId1"/>
@@ -138,7 +138,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="90">
   <si>
     <t>雇员ID</t>
   </si>
@@ -309,6 +309,96 @@
   </si>
   <si>
     <t>阿尔弗雷德</t>
+  </si>
+  <si>
+    <t>1026002_1126002_2</t>
+  </si>
+  <si>
+    <t>艾拉</t>
+  </si>
+  <si>
+    <t>1026102_1126102_4</t>
+  </si>
+  <si>
+    <t>艾玛</t>
+  </si>
+  <si>
+    <t>1026202_1126202_6</t>
+  </si>
+  <si>
+    <t>艾娃</t>
+  </si>
+  <si>
+    <t>1026302_1126302_8</t>
+  </si>
+  <si>
+    <t>安娜</t>
+  </si>
+  <si>
+    <t>1026402_1126402_10</t>
+  </si>
+  <si>
+    <t>哈珀</t>
+  </si>
+  <si>
+    <t>1027002_1127002_2</t>
+  </si>
+  <si>
+    <t>伊芙琳</t>
+  </si>
+  <si>
+    <t>1027102_1127102_4</t>
+  </si>
+  <si>
+    <t>夏洛特</t>
+  </si>
+  <si>
+    <t>1027202_1127202_6</t>
+  </si>
+  <si>
+    <t>斯嘉丽</t>
+  </si>
+  <si>
+    <t>1027302_1127302_8</t>
+  </si>
+  <si>
+    <t>莉莉安</t>
+  </si>
+  <si>
+    <t>1027402_1127402_10</t>
+  </si>
+  <si>
+    <t>克拉拉</t>
+  </si>
+  <si>
+    <t>1028002_1128002_2</t>
+  </si>
+  <si>
+    <t>奥利维亚</t>
+  </si>
+  <si>
+    <t>1028102_1128102_4</t>
+  </si>
+  <si>
+    <t>玛格丽特</t>
+  </si>
+  <si>
+    <t>1028202_1128202_6</t>
+  </si>
+  <si>
+    <t>维奥莱特</t>
+  </si>
+  <si>
+    <t>1028302_1128302_8</t>
+  </si>
+  <si>
+    <t>维多利亚</t>
+  </si>
+  <si>
+    <t>1028402_1128402_10</t>
+  </si>
+  <si>
+    <t>伊丽莎白</t>
   </si>
   <si>
     <t>道具ID</t>
@@ -1554,7 +1644,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.75" style="4" customWidth="1"/>
@@ -1710,7 +1800,7 @@
         <v>23</v>
       </c>
       <c r="D6" s="1">
-        <v>1026002</v>
+        <v>1026101</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>24</v>
@@ -1743,7 +1833,7 @@
         <v>26</v>
       </c>
       <c r="D7" s="1">
-        <v>1026101</v>
+        <v>1026201</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>27</v>
@@ -1776,7 +1866,7 @@
         <v>29</v>
       </c>
       <c r="D8" s="1">
-        <v>1026102</v>
+        <v>1026302</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>30</v>
@@ -1809,7 +1899,7 @@
         <v>32</v>
       </c>
       <c r="D9" s="1">
-        <v>1026201</v>
+        <v>1026401</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>33</v>
@@ -1842,7 +1932,7 @@
         <v>35</v>
       </c>
       <c r="D10" s="1">
-        <v>1026202</v>
+        <v>1027001</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>36</v>
@@ -1875,7 +1965,7 @@
         <v>38</v>
       </c>
       <c r="D11" s="1">
-        <v>1026301</v>
+        <v>1027101</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>39</v>
@@ -1908,7 +1998,7 @@
         <v>40</v>
       </c>
       <c r="D12" s="1">
-        <v>1026302</v>
+        <v>1027201</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>41</v>
@@ -1941,7 +2031,7 @@
         <v>42</v>
       </c>
       <c r="D13" s="1">
-        <v>1026401</v>
+        <v>1027301</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>43</v>
@@ -1974,7 +2064,7 @@
         <v>44</v>
       </c>
       <c r="D14" s="1">
-        <v>1026402</v>
+        <v>1027401</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>45</v>
@@ -2007,7 +2097,7 @@
         <v>46</v>
       </c>
       <c r="D15" s="1">
-        <v>1027001</v>
+        <v>1028001</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>47</v>
@@ -2040,7 +2130,7 @@
         <v>49</v>
       </c>
       <c r="D16" s="1">
-        <v>1027002</v>
+        <v>1028101</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>50</v>
@@ -2073,7 +2163,7 @@
         <v>51</v>
       </c>
       <c r="D17" s="1">
-        <v>1027101</v>
+        <v>1028201</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>52</v>
@@ -2106,7 +2196,7 @@
         <v>53</v>
       </c>
       <c r="D18" s="1">
-        <v>1027102</v>
+        <v>1028301</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>54</v>
@@ -2139,7 +2229,7 @@
         <v>55</v>
       </c>
       <c r="D19" s="1">
-        <v>1027201</v>
+        <v>1028401</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>56</v>
@@ -2157,6 +2247,501 @@
         <v>300202</v>
       </c>
       <c r="J19" s="12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="6">
+        <f t="shared" ref="A20:A34" si="1">F20*10000+H20*1000+B20</f>
+        <v>101016</v>
+      </c>
+      <c r="B20" s="11">
+        <v>16</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1026002</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" s="11">
+        <v>10</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="H20" s="11">
+        <v>1</v>
+      </c>
+      <c r="I20" s="10">
+        <v>100101</v>
+      </c>
+      <c r="J20" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="6">
+        <f t="shared" si="1"/>
+        <v>102017</v>
+      </c>
+      <c r="B21" s="11">
+        <v>17</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1026102</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F21" s="11">
+        <v>10</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="H21" s="11">
+        <v>2</v>
+      </c>
+      <c r="I21" s="10">
+        <v>100102</v>
+      </c>
+      <c r="J21" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="6">
+        <f t="shared" si="1"/>
+        <v>103018</v>
+      </c>
+      <c r="B22" s="11">
+        <v>18</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1026202</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F22" s="11">
+        <v>10</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="H22" s="11">
+        <v>3</v>
+      </c>
+      <c r="I22" s="10">
+        <v>100103</v>
+      </c>
+      <c r="J22" s="11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="6">
+        <f t="shared" si="1"/>
+        <v>104019</v>
+      </c>
+      <c r="B23" s="11">
+        <v>19</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1026302</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F23" s="11">
+        <v>10</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="H23" s="11">
+        <v>4</v>
+      </c>
+      <c r="I23" s="10">
+        <v>100201</v>
+      </c>
+      <c r="J23" s="12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="6">
+        <f t="shared" si="1"/>
+        <v>105020</v>
+      </c>
+      <c r="B24" s="11">
+        <v>20</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1026402</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F24" s="11">
+        <v>10</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="H24" s="11">
+        <v>5</v>
+      </c>
+      <c r="I24" s="10">
+        <v>100202</v>
+      </c>
+      <c r="J24" s="12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="6">
+        <f t="shared" si="1"/>
+        <v>201021</v>
+      </c>
+      <c r="B25" s="11">
+        <v>21</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1027002</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F25" s="6">
+        <v>20</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H25" s="12">
+        <v>1</v>
+      </c>
+      <c r="I25" s="10">
+        <v>200101</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="6">
+        <f t="shared" si="1"/>
+        <v>202022</v>
+      </c>
+      <c r="B26" s="11">
+        <v>22</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1027102</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F26" s="6">
+        <v>20</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H26" s="12">
+        <v>2</v>
+      </c>
+      <c r="I26" s="10">
+        <v>200102</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="6">
+        <f t="shared" si="1"/>
+        <v>203023</v>
+      </c>
+      <c r="B27" s="11">
+        <v>23</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1027202</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F27" s="6">
+        <v>20</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H27" s="12">
+        <v>3</v>
+      </c>
+      <c r="I27" s="10">
+        <v>200103</v>
+      </c>
+      <c r="J27" s="11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="6">
+        <f t="shared" si="1"/>
+        <v>204024</v>
+      </c>
+      <c r="B28" s="11">
+        <v>24</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1027302</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F28" s="6">
+        <v>20</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H28" s="12">
+        <v>4</v>
+      </c>
+      <c r="I28" s="10">
+        <v>200201</v>
+      </c>
+      <c r="J28" s="12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="6">
+        <f t="shared" si="1"/>
+        <v>205025</v>
+      </c>
+      <c r="B29" s="11">
+        <v>25</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1027402</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F29" s="6">
+        <v>20</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H29" s="12">
+        <v>5</v>
+      </c>
+      <c r="I29" s="10">
+        <v>200202</v>
+      </c>
+      <c r="J29" s="12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="6">
+        <f t="shared" si="1"/>
+        <v>301026</v>
+      </c>
+      <c r="B30" s="11">
+        <v>26</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1028002</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F30" s="6">
+        <v>30</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H30" s="6">
+        <v>1</v>
+      </c>
+      <c r="I30" s="10">
+        <v>300101</v>
+      </c>
+      <c r="J30" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="6">
+        <f t="shared" si="1"/>
+        <v>302027</v>
+      </c>
+      <c r="B31" s="11">
+        <v>27</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1028102</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F31" s="6">
+        <v>30</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H31" s="6">
+        <v>2</v>
+      </c>
+      <c r="I31" s="10">
+        <v>300102</v>
+      </c>
+      <c r="J31" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="6">
+        <f t="shared" si="1"/>
+        <v>303028</v>
+      </c>
+      <c r="B32" s="11">
+        <v>28</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1028202</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F32" s="6">
+        <v>30</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H32" s="6">
+        <v>3</v>
+      </c>
+      <c r="I32" s="10">
+        <v>300103</v>
+      </c>
+      <c r="J32" s="11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="6">
+        <f t="shared" si="1"/>
+        <v>304029</v>
+      </c>
+      <c r="B33" s="11">
+        <v>29</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D33" s="1">
+        <v>1028302</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F33" s="6">
+        <v>30</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H33" s="6">
+        <v>4</v>
+      </c>
+      <c r="I33" s="10">
+        <v>300201</v>
+      </c>
+      <c r="J33" s="12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="6">
+        <f t="shared" si="1"/>
+        <v>305030</v>
+      </c>
+      <c r="B34" s="11">
+        <v>30</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D34" s="1">
+        <v>1028402</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F34" s="6">
+        <v>30</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H34" s="6">
+        <v>5</v>
+      </c>
+      <c r="I34" s="10">
+        <v>300202</v>
+      </c>
+      <c r="J34" s="12" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2175,13 +2760,13 @@
   <sheetData>
     <row r="11" spans="4:8">
       <c r="D11" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="E11" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="4:8">

--- a/hall/resources/sample/EmployeeProfile.xlsx
+++ b/hall/resources/sample/EmployeeProfile.xlsx
@@ -585,12 +585,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1782,7 +1782,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="10">
-        <v>100101</v>
+        <v>100103</v>
       </c>
       <c r="J5" s="11" t="s">
         <v>22</v>
@@ -1815,7 +1815,7 @@
         <v>2</v>
       </c>
       <c r="I6" s="10">
-        <v>100102</v>
+        <v>100103</v>
       </c>
       <c r="J6" s="11" t="s">
         <v>25</v>
@@ -1881,7 +1881,7 @@
         <v>4</v>
       </c>
       <c r="I8" s="10">
-        <v>100201</v>
+        <v>100103</v>
       </c>
       <c r="J8" s="12" t="s">
         <v>31</v>
@@ -1914,7 +1914,7 @@
         <v>5</v>
       </c>
       <c r="I9" s="10">
-        <v>100202</v>
+        <v>100103</v>
       </c>
       <c r="J9" s="12" t="s">
         <v>34</v>
@@ -1947,7 +1947,7 @@
         <v>1</v>
       </c>
       <c r="I10" s="10">
-        <v>200101</v>
+        <v>200102</v>
       </c>
       <c r="J10" s="11" t="s">
         <v>22</v>
@@ -2013,7 +2013,7 @@
         <v>3</v>
       </c>
       <c r="I12" s="10">
-        <v>200103</v>
+        <v>200102</v>
       </c>
       <c r="J12" s="11" t="s">
         <v>28</v>
@@ -2046,7 +2046,7 @@
         <v>4</v>
       </c>
       <c r="I13" s="10">
-        <v>200201</v>
+        <v>200102</v>
       </c>
       <c r="J13" s="12" t="s">
         <v>31</v>
@@ -2079,7 +2079,7 @@
         <v>5</v>
       </c>
       <c r="I14" s="10">
-        <v>200202</v>
+        <v>200102</v>
       </c>
       <c r="J14" s="12" t="s">
         <v>34</v>
@@ -2112,7 +2112,7 @@
         <v>1</v>
       </c>
       <c r="I15" s="10">
-        <v>300101</v>
+        <v>300103</v>
       </c>
       <c r="J15" s="11" t="s">
         <v>22</v>
@@ -2145,7 +2145,7 @@
         <v>2</v>
       </c>
       <c r="I16" s="10">
-        <v>300102</v>
+        <v>300103</v>
       </c>
       <c r="J16" s="11" t="s">
         <v>25</v>
@@ -2211,7 +2211,7 @@
         <v>4</v>
       </c>
       <c r="I18" s="10">
-        <v>300201</v>
+        <v>300103</v>
       </c>
       <c r="J18" s="12" t="s">
         <v>31</v>
@@ -2244,7 +2244,7 @@
         <v>5</v>
       </c>
       <c r="I19" s="10">
-        <v>300202</v>
+        <v>300103</v>
       </c>
       <c r="J19" s="12" t="s">
         <v>34</v>
@@ -2277,7 +2277,7 @@
         <v>1</v>
       </c>
       <c r="I20" s="10">
-        <v>100101</v>
+        <v>100103</v>
       </c>
       <c r="J20" s="11" t="s">
         <v>22</v>
@@ -2310,7 +2310,7 @@
         <v>2</v>
       </c>
       <c r="I21" s="10">
-        <v>100102</v>
+        <v>100103</v>
       </c>
       <c r="J21" s="11" t="s">
         <v>25</v>
@@ -2376,7 +2376,7 @@
         <v>4</v>
       </c>
       <c r="I23" s="10">
-        <v>100201</v>
+        <v>100103</v>
       </c>
       <c r="J23" s="12" t="s">
         <v>31</v>
@@ -2409,7 +2409,7 @@
         <v>5</v>
       </c>
       <c r="I24" s="10">
-        <v>100202</v>
+        <v>100103</v>
       </c>
       <c r="J24" s="12" t="s">
         <v>34</v>
@@ -2442,7 +2442,7 @@
         <v>1</v>
       </c>
       <c r="I25" s="10">
-        <v>200101</v>
+        <v>200102</v>
       </c>
       <c r="J25" s="11" t="s">
         <v>22</v>
@@ -2508,7 +2508,7 @@
         <v>3</v>
       </c>
       <c r="I27" s="10">
-        <v>200103</v>
+        <v>200102</v>
       </c>
       <c r="J27" s="11" t="s">
         <v>28</v>
@@ -2541,7 +2541,7 @@
         <v>4</v>
       </c>
       <c r="I28" s="10">
-        <v>200201</v>
+        <v>200102</v>
       </c>
       <c r="J28" s="12" t="s">
         <v>31</v>
@@ -2574,7 +2574,7 @@
         <v>5</v>
       </c>
       <c r="I29" s="10">
-        <v>200202</v>
+        <v>200102</v>
       </c>
       <c r="J29" s="12" t="s">
         <v>34</v>
@@ -2607,7 +2607,7 @@
         <v>1</v>
       </c>
       <c r="I30" s="10">
-        <v>300101</v>
+        <v>300103</v>
       </c>
       <c r="J30" s="11" t="s">
         <v>22</v>
@@ -2640,7 +2640,7 @@
         <v>2</v>
       </c>
       <c r="I31" s="10">
-        <v>300102</v>
+        <v>300103</v>
       </c>
       <c r="J31" s="11" t="s">
         <v>25</v>
@@ -2706,7 +2706,7 @@
         <v>4</v>
       </c>
       <c r="I33" s="10">
-        <v>300201</v>
+        <v>300103</v>
       </c>
       <c r="J33" s="12" t="s">
         <v>31</v>
@@ -2739,7 +2739,7 @@
         <v>5</v>
       </c>
       <c r="I34" s="10">
-        <v>300202</v>
+        <v>300103</v>
       </c>
       <c r="J34" s="12" t="s">
         <v>34</v>

--- a/hall/resources/sample/EmployeeProfile.xlsx
+++ b/hall/resources/sample/EmployeeProfile.xlsx
@@ -209,7 +209,7 @@
     <t>初级</t>
   </si>
   <si>
-    <t>1026101_1126101_4</t>
+    <t>1026101_1126101_2</t>
   </si>
   <si>
     <t>亨利</t>
@@ -218,7 +218,7 @@
     <t>中级</t>
   </si>
   <si>
-    <t>1026201_1126201_6</t>
+    <t>1026201_1126201_2</t>
   </si>
   <si>
     <t>乔治</t>
@@ -227,7 +227,7 @@
     <t>高级</t>
   </si>
   <si>
-    <t>1026301_1126301_8</t>
+    <t>1026301_1126301_2</t>
   </si>
   <si>
     <t>亚瑟</t>
@@ -236,7 +236,7 @@
     <t>金牌</t>
   </si>
   <si>
-    <t>1026401_1126401_10</t>
+    <t>1026401_1126401_2</t>
   </si>
   <si>
     <t>马修</t>
@@ -254,25 +254,25 @@
     <t>服务员</t>
   </si>
   <si>
-    <t>1027101_1127101_4</t>
+    <t>1027101_1127101_2</t>
   </si>
   <si>
     <t>埃米尔</t>
   </si>
   <si>
-    <t>1027201_1127201_6</t>
+    <t>1027201_1127201_2</t>
   </si>
   <si>
     <t>雷蒙德</t>
   </si>
   <si>
-    <t>1027301_1127301_8</t>
+    <t>1027301_1127301_2</t>
   </si>
   <si>
     <t>丹尼尔</t>
   </si>
   <si>
-    <t>1027401_1127401_10</t>
+    <t>1027401_1127401_2</t>
   </si>
   <si>
     <t>卢卡斯</t>
@@ -287,25 +287,25 @@
     <t>管理员</t>
   </si>
   <si>
-    <t>1028101_1128101_4</t>
+    <t>1028101_1128101_2</t>
   </si>
   <si>
     <t>亚历山大</t>
   </si>
   <si>
-    <t>1028201_1128201_6</t>
+    <t>1028201_1128201_2</t>
   </si>
   <si>
     <t>奥古斯特</t>
   </si>
   <si>
-    <t>1028301_1128301_8</t>
+    <t>1028301_1128301_2</t>
   </si>
   <si>
     <t>费利克斯</t>
   </si>
   <si>
-    <t>1028401_1128401_10</t>
+    <t>1028401_1128401_2</t>
   </si>
   <si>
     <t>阿尔弗雷德</t>
@@ -317,25 +317,25 @@
     <t>艾拉</t>
   </si>
   <si>
-    <t>1026102_1126102_4</t>
+    <t>1026102_1126102_2</t>
   </si>
   <si>
     <t>艾玛</t>
   </si>
   <si>
-    <t>1026202_1126202_6</t>
+    <t>1026202_1126202_2</t>
   </si>
   <si>
     <t>艾娃</t>
   </si>
   <si>
-    <t>1026302_1126302_8</t>
+    <t>1026302_1126302_2</t>
   </si>
   <si>
     <t>安娜</t>
   </si>
   <si>
-    <t>1026402_1126402_10</t>
+    <t>1026402_1126402_2</t>
   </si>
   <si>
     <t>哈珀</t>
@@ -347,25 +347,25 @@
     <t>伊芙琳</t>
   </si>
   <si>
-    <t>1027102_1127102_4</t>
+    <t>1027102_1127102_2</t>
   </si>
   <si>
     <t>夏洛特</t>
   </si>
   <si>
-    <t>1027202_1127202_6</t>
+    <t>1027202_1127202_2</t>
   </si>
   <si>
     <t>斯嘉丽</t>
   </si>
   <si>
-    <t>1027302_1127302_8</t>
+    <t>1027302_1127302_2</t>
   </si>
   <si>
     <t>莉莉安</t>
   </si>
   <si>
-    <t>1027402_1127402_10</t>
+    <t>1027402_1127402_2</t>
   </si>
   <si>
     <t>克拉拉</t>
@@ -377,25 +377,25 @@
     <t>奥利维亚</t>
   </si>
   <si>
-    <t>1028102_1128102_4</t>
+    <t>1028102_1128102_2</t>
   </si>
   <si>
     <t>玛格丽特</t>
   </si>
   <si>
-    <t>1028202_1128202_6</t>
+    <t>1028202_1128202_2</t>
   </si>
   <si>
     <t>维奥莱特</t>
   </si>
   <si>
-    <t>1028302_1128302_8</t>
+    <t>1028302_1128302_2</t>
   </si>
   <si>
     <t>维多利亚</t>
   </si>
   <si>
-    <t>1028402_1128402_10</t>
+    <t>1028402_1128402_2</t>
   </si>
   <si>
     <t>伊丽莎白</t>

--- a/hall/resources/sample/EmployeeProfile.xlsx
+++ b/hall/resources/sample/EmployeeProfile.xlsx
@@ -52,6 +52,28 @@
           </rPr>
           <t xml:space="preserve">
 </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+每个雇员都带有技能，但是这个技能不会生效；只有当这个雇员被设置为主管后，这个技能才会产生加成</t>
         </r>
       </text>
     </comment>
@@ -585,12 +607,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/hall/resources/sample/EmployeeProfile.xlsx
+++ b/hall/resources/sample/EmployeeProfile.xlsx
@@ -219,7 +219,7 @@
     <t>SkillIdList</t>
   </si>
   <si>
-    <t>1026001_1126001_2</t>
+    <t>1026001_1126001_10</t>
   </si>
   <si>
     <t>威廉</t>
@@ -231,7 +231,7 @@
     <t>初级</t>
   </si>
   <si>
-    <t>1026101_1126101_2</t>
+    <t>1026101_1126101_10</t>
   </si>
   <si>
     <t>亨利</t>
@@ -240,7 +240,7 @@
     <t>中级</t>
   </si>
   <si>
-    <t>1026201_1126201_2</t>
+    <t>1026201_1126201_10</t>
   </si>
   <si>
     <t>乔治</t>
@@ -249,7 +249,7 @@
     <t>高级</t>
   </si>
   <si>
-    <t>1026301_1126301_2</t>
+    <t>1026301_1126301_10</t>
   </si>
   <si>
     <t>亚瑟</t>
@@ -258,7 +258,7 @@
     <t>金牌</t>
   </si>
   <si>
-    <t>1026401_1126401_2</t>
+    <t>1026401_1126401_10</t>
   </si>
   <si>
     <t>马修</t>
@@ -267,7 +267,7 @@
     <t>王牌</t>
   </si>
   <si>
-    <t>1027001_1127001_2</t>
+    <t>1027001_1127001_10</t>
   </si>
   <si>
     <t>拉斐尔</t>
@@ -276,31 +276,31 @@
     <t>服务员</t>
   </si>
   <si>
-    <t>1027101_1127101_2</t>
+    <t>1027101_1127101_10</t>
   </si>
   <si>
     <t>埃米尔</t>
   </si>
   <si>
-    <t>1027201_1127201_2</t>
+    <t>1027201_1127201_10</t>
   </si>
   <si>
     <t>雷蒙德</t>
   </si>
   <si>
-    <t>1027301_1127301_2</t>
+    <t>1027301_1127301_10</t>
   </si>
   <si>
     <t>丹尼尔</t>
   </si>
   <si>
-    <t>1027401_1127401_2</t>
+    <t>1027401_1127401_10</t>
   </si>
   <si>
     <t>卢卡斯</t>
   </si>
   <si>
-    <t>1028001_1128001_2</t>
+    <t>1028001_1128001_10</t>
   </si>
   <si>
     <t>尼古拉斯</t>
@@ -309,115 +309,115 @@
     <t>管理员</t>
   </si>
   <si>
-    <t>1028101_1128101_2</t>
+    <t>1028101_1128101_10</t>
   </si>
   <si>
     <t>亚历山大</t>
   </si>
   <si>
-    <t>1028201_1128201_2</t>
+    <t>1028201_1128201_10</t>
   </si>
   <si>
     <t>奥古斯特</t>
   </si>
   <si>
-    <t>1028301_1128301_2</t>
+    <t>1028301_1128301_10</t>
   </si>
   <si>
     <t>费利克斯</t>
   </si>
   <si>
-    <t>1028401_1128401_2</t>
+    <t>1028401_1128401_10</t>
   </si>
   <si>
     <t>阿尔弗雷德</t>
   </si>
   <si>
-    <t>1026002_1126002_2</t>
+    <t>1026002_1126002_10</t>
   </si>
   <si>
     <t>艾拉</t>
   </si>
   <si>
-    <t>1026102_1126102_2</t>
+    <t>1026102_1126102_10</t>
   </si>
   <si>
     <t>艾玛</t>
   </si>
   <si>
-    <t>1026202_1126202_2</t>
+    <t>1026202_1126202_10</t>
   </si>
   <si>
     <t>艾娃</t>
   </si>
   <si>
-    <t>1026302_1126302_2</t>
+    <t>1026302_1126302_10</t>
   </si>
   <si>
     <t>安娜</t>
   </si>
   <si>
-    <t>1026402_1126402_2</t>
+    <t>1026402_1126402_10</t>
   </si>
   <si>
     <t>哈珀</t>
   </si>
   <si>
-    <t>1027002_1127002_2</t>
+    <t>1027002_1127002_10</t>
   </si>
   <si>
     <t>伊芙琳</t>
   </si>
   <si>
-    <t>1027102_1127102_2</t>
+    <t>1027102_1127102_10</t>
   </si>
   <si>
     <t>夏洛特</t>
   </si>
   <si>
-    <t>1027202_1127202_2</t>
+    <t>1027202_1127202_10</t>
   </si>
   <si>
     <t>斯嘉丽</t>
   </si>
   <si>
-    <t>1027302_1127302_2</t>
+    <t>1027302_1127302_10</t>
   </si>
   <si>
     <t>莉莉安</t>
   </si>
   <si>
-    <t>1027402_1127402_2</t>
+    <t>1027402_1127402_10</t>
   </si>
   <si>
     <t>克拉拉</t>
   </si>
   <si>
-    <t>1028002_1128002_2</t>
+    <t>1028002_1128002_10</t>
   </si>
   <si>
     <t>奥利维亚</t>
   </si>
   <si>
-    <t>1028102_1128102_2</t>
+    <t>1028102_1128102_10</t>
   </si>
   <si>
     <t>玛格丽特</t>
   </si>
   <si>
-    <t>1028202_1128202_2</t>
+    <t>1028202_1128202_10</t>
   </si>
   <si>
     <t>维奥莱特</t>
   </si>
   <si>
-    <t>1028302_1128302_2</t>
+    <t>1028302_1128302_10</t>
   </si>
   <si>
     <t>维多利亚</t>
   </si>
   <si>
-    <t>1028402_1128402_2</t>
+    <t>1028402_1128402_10</t>
   </si>
   <si>
     <t>伊丽莎白</t>

--- a/hall/resources/sample/EmployeeProfile.xlsx
+++ b/hall/resources/sample/EmployeeProfile.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
@@ -442,7 +447,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -461,6 +466,13 @@
       <color rgb="FF212529"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -971,137 +983,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1137,6 +1149,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1791,7 +1806,7 @@
       <c r="D5" s="1">
         <v>1026001</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="12" t="s">
         <v>20</v>
       </c>
       <c r="F5" s="11">
@@ -1905,7 +1920,7 @@
       <c r="I8" s="10">
         <v>100103</v>
       </c>
-      <c r="J8" s="12" t="s">
+      <c r="J8" s="13" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1938,7 +1953,7 @@
       <c r="I9" s="10">
         <v>100103</v>
       </c>
-      <c r="J9" s="12" t="s">
+      <c r="J9" s="13" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1956,7 +1971,7 @@
       <c r="D10" s="1">
         <v>1027001</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="12" t="s">
         <v>36</v>
       </c>
       <c r="F10" s="6">
@@ -1965,7 +1980,7 @@
       <c r="G10" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="13">
         <v>1</v>
       </c>
       <c r="I10" s="10">
@@ -1998,7 +2013,7 @@
       <c r="G11" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="13">
         <v>2</v>
       </c>
       <c r="I11" s="10">
@@ -2031,7 +2046,7 @@
       <c r="G12" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="13">
         <v>3</v>
       </c>
       <c r="I12" s="10">
@@ -2064,13 +2079,13 @@
       <c r="G13" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="13">
         <v>4</v>
       </c>
       <c r="I13" s="10">
         <v>200102</v>
       </c>
-      <c r="J13" s="12" t="s">
+      <c r="J13" s="13" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2097,13 +2112,13 @@
       <c r="G14" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="13">
         <v>5</v>
       </c>
       <c r="I14" s="10">
         <v>200102</v>
       </c>
-      <c r="J14" s="12" t="s">
+      <c r="J14" s="13" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2235,7 +2250,7 @@
       <c r="I18" s="10">
         <v>300103</v>
       </c>
-      <c r="J18" s="12" t="s">
+      <c r="J18" s="13" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2268,7 +2283,7 @@
       <c r="I19" s="10">
         <v>300103</v>
       </c>
-      <c r="J19" s="12" t="s">
+      <c r="J19" s="13" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2352,7 +2367,7 @@
       <c r="D22" s="1">
         <v>1026202</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="12" t="s">
         <v>62</v>
       </c>
       <c r="F22" s="11">
@@ -2400,7 +2415,7 @@
       <c r="I23" s="10">
         <v>100103</v>
       </c>
-      <c r="J23" s="12" t="s">
+      <c r="J23" s="13" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2433,7 +2448,7 @@
       <c r="I24" s="10">
         <v>100103</v>
       </c>
-      <c r="J24" s="12" t="s">
+      <c r="J24" s="13" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2460,7 +2475,7 @@
       <c r="G25" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="H25" s="12">
+      <c r="H25" s="13">
         <v>1</v>
       </c>
       <c r="I25" s="10">
@@ -2493,7 +2508,7 @@
       <c r="G26" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="H26" s="12">
+      <c r="H26" s="13">
         <v>2</v>
       </c>
       <c r="I26" s="10">
@@ -2526,7 +2541,7 @@
       <c r="G27" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="H27" s="12">
+      <c r="H27" s="13">
         <v>3</v>
       </c>
       <c r="I27" s="10">
@@ -2559,13 +2574,13 @@
       <c r="G28" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="H28" s="12">
+      <c r="H28" s="13">
         <v>4</v>
       </c>
       <c r="I28" s="10">
         <v>200102</v>
       </c>
-      <c r="J28" s="12" t="s">
+      <c r="J28" s="13" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2583,7 +2598,7 @@
       <c r="D29" s="1">
         <v>1027402</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F29" s="6">
@@ -2592,13 +2607,13 @@
       <c r="G29" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="H29" s="12">
+      <c r="H29" s="13">
         <v>5</v>
       </c>
       <c r="I29" s="10">
         <v>200102</v>
       </c>
-      <c r="J29" s="12" t="s">
+      <c r="J29" s="13" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2616,7 +2631,7 @@
       <c r="D30" s="1">
         <v>1028002</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E30" s="12" t="s">
         <v>78</v>
       </c>
       <c r="F30" s="6">
@@ -2649,7 +2664,7 @@
       <c r="D31" s="1">
         <v>1028102</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E31" s="12" t="s">
         <v>80</v>
       </c>
       <c r="F31" s="6">
@@ -2730,7 +2745,7 @@
       <c r="I33" s="10">
         <v>300103</v>
       </c>
-      <c r="J33" s="12" t="s">
+      <c r="J33" s="13" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2763,7 +2778,7 @@
       <c r="I34" s="10">
         <v>300103</v>
       </c>
-      <c r="J34" s="12" t="s">
+      <c r="J34" s="13" t="s">
         <v>34</v>
       </c>
     </row>

--- a/hall/resources/sample/EmployeeProfile.xlsx
+++ b/hall/resources/sample/EmployeeProfile.xlsx
@@ -447,7 +447,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -470,6 +470,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -983,137 +990,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1155,6 +1162,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2367,7 +2377,7 @@
       <c r="D22" s="1">
         <v>1026202</v>
       </c>
-      <c r="E22" s="12" t="s">
+      <c r="E22" s="1" t="s">
         <v>62</v>
       </c>
       <c r="F22" s="11">
@@ -2466,7 +2476,7 @@
       <c r="D25" s="1">
         <v>1027002</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" s="14" t="s">
         <v>68</v>
       </c>
       <c r="F25" s="6">

--- a/hall/resources/sample/EmployeeProfile.xlsx
+++ b/hall/resources/sample/EmployeeProfile.xlsx
@@ -1433,6 +1433,11 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
+  <colors>
+    <mruColors>
+      <color rgb="00FF0000"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1849,7 +1854,7 @@
       <c r="D6" s="1">
         <v>1026101</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="12" t="s">
         <v>24</v>
       </c>
       <c r="F6" s="11">
@@ -1882,7 +1887,7 @@
       <c r="D7" s="1">
         <v>1026201</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="12" t="s">
         <v>27</v>
       </c>
       <c r="F7" s="11">
@@ -1915,7 +1920,7 @@
       <c r="D8" s="1">
         <v>1026302</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="12" t="s">
         <v>30</v>
       </c>
       <c r="F8" s="11">
@@ -1948,7 +1953,7 @@
       <c r="D9" s="1">
         <v>1026401</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="12" t="s">
         <v>33</v>
       </c>
       <c r="F9" s="11">
@@ -2014,7 +2019,7 @@
       <c r="D11" s="1">
         <v>1027101</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="12" t="s">
         <v>39</v>
       </c>
       <c r="F11" s="6">
@@ -2047,7 +2052,7 @@
       <c r="D12" s="1">
         <v>1027201</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="12" t="s">
         <v>41</v>
       </c>
       <c r="F12" s="6">
@@ -2080,7 +2085,7 @@
       <c r="D13" s="1">
         <v>1027301</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="12" t="s">
         <v>43</v>
       </c>
       <c r="F13" s="6">
@@ -2113,7 +2118,7 @@
       <c r="D14" s="1">
         <v>1027401</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="12" t="s">
         <v>45</v>
       </c>
       <c r="F14" s="6">
@@ -2146,7 +2151,7 @@
       <c r="D15" s="1">
         <v>1028001</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="12" t="s">
         <v>47</v>
       </c>
       <c r="F15" s="6">
@@ -2179,7 +2184,7 @@
       <c r="D16" s="1">
         <v>1028101</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="12" t="s">
         <v>50</v>
       </c>
       <c r="F16" s="6">
@@ -2212,7 +2217,7 @@
       <c r="D17" s="1">
         <v>1028201</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="12" t="s">
         <v>52</v>
       </c>
       <c r="F17" s="6">
@@ -2245,7 +2250,7 @@
       <c r="D18" s="1">
         <v>1028301</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="12" t="s">
         <v>54</v>
       </c>
       <c r="F18" s="6">
@@ -2278,7 +2283,7 @@
       <c r="D19" s="1">
         <v>1028401</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" s="12" t="s">
         <v>56</v>
       </c>
       <c r="F19" s="6">
@@ -2509,7 +2514,7 @@
       <c r="D26" s="1">
         <v>1027102</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" s="12" t="s">
         <v>70</v>
       </c>
       <c r="F26" s="6">
@@ -2542,7 +2547,7 @@
       <c r="D27" s="1">
         <v>1027202</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E27" s="12" t="s">
         <v>72</v>
       </c>
       <c r="F27" s="6">
@@ -2575,7 +2580,7 @@
       <c r="D28" s="1">
         <v>1027302</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" s="12" t="s">
         <v>74</v>
       </c>
       <c r="F28" s="6">
@@ -2707,7 +2712,7 @@
       <c r="D32" s="1">
         <v>1028202</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E32" s="12" t="s">
         <v>82</v>
       </c>
       <c r="F32" s="6">
@@ -2740,7 +2745,7 @@
       <c r="D33" s="1">
         <v>1028302</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" s="12" t="s">
         <v>84</v>
       </c>
       <c r="F33" s="6">
@@ -2773,7 +2778,7 @@
       <c r="D34" s="1">
         <v>1028402</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E34" s="12" t="s">
         <v>86</v>
       </c>
       <c r="F34" s="6">

--- a/hall/resources/sample/EmployeeProfile.xlsx
+++ b/hall/resources/sample/EmployeeProfile.xlsx
@@ -165,7 +165,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
   <si>
     <t>雇员ID</t>
   </si>
@@ -197,6 +197,9 @@
     <t>品质名称备注</t>
   </si>
   <si>
+    <t>雇员描述多语言</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -222,6 +225,9 @@
   </si>
   <si>
     <t>SkillIdList</t>
+  </si>
+  <si>
+    <t>language</t>
   </si>
   <si>
     <t>1026001_1126001_10</t>
@@ -447,7 +453,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -473,6 +479,11 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -990,137 +1001,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1145,6 +1156,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1160,10 +1174,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1696,7 +1713,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.75" style="4" customWidth="1"/>
@@ -1709,9 +1726,10 @@
     <col min="8" max="8" width="16.875" style="4" customWidth="1"/>
     <col min="9" max="9" width="21.25" style="5" customWidth="1"/>
     <col min="10" max="10" width="21.75" style="4" customWidth="1"/>
+    <col min="11" max="11" width="16.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1742,60 +1760,69 @@
       <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>10</v>
+      <c r="C2" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>11</v>
       </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2" s="6"/>
       <c r="H2" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" s="9" t="s">
         <v>11</v>
       </c>
+      <c r="I2" s="10" t="s">
+        <v>12</v>
+      </c>
       <c r="J2" s="6"/>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="K2" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" s="6"/>
       <c r="H3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="10" t="s">
         <v>18</v>
       </c>
+      <c r="I3" s="11" t="s">
+        <v>19</v>
+      </c>
       <c r="J3" s="6"/>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="K3" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1804,997 +1831,1088 @@
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
-      <c r="I4" s="10"/>
+      <c r="I4" s="11"/>
       <c r="J4" s="6"/>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="K4" s="8"/>
+    </row>
+    <row r="5" ht="16.5" spans="1:11">
       <c r="A5" s="6">
         <f>F5*10000+H5*1000+B5</f>
         <v>101001</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="12">
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D5" s="1">
         <v>1026001</v>
       </c>
-      <c r="E5" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="11">
+      <c r="E5" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="12">
         <v>10</v>
       </c>
-      <c r="G5" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="11">
+      <c r="G5" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="12">
         <v>1</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="11">
         <v>100103</v>
       </c>
-      <c r="J5" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="J5" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="14">
+        <v>2026001</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" spans="1:11">
       <c r="A6" s="6">
         <f t="shared" ref="A6:A19" si="0">F6*10000+H6*1000+B6</f>
         <v>102002</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="12">
         <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D6" s="1">
         <v>1026101</v>
       </c>
-      <c r="E6" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="11">
+      <c r="E6" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="12">
         <v>10</v>
       </c>
-      <c r="G6" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="11">
+      <c r="G6" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="12">
         <v>2</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="11">
         <v>100103</v>
       </c>
-      <c r="J6" s="11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+      <c r="J6" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="K6" s="14">
+        <v>2026101</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" spans="1:11">
       <c r="A7" s="6">
         <f t="shared" si="0"/>
         <v>103003</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="12">
         <v>3</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D7" s="1">
         <v>1026201</v>
       </c>
-      <c r="E7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="11">
+      <c r="E7" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="12">
         <v>10</v>
       </c>
-      <c r="G7" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" s="11">
+      <c r="G7" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="12">
         <v>3</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="11">
         <v>100103</v>
       </c>
-      <c r="J7" s="11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+      <c r="J7" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="K7" s="14">
+        <v>2026201</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" spans="1:11">
       <c r="A8" s="6">
         <f t="shared" si="0"/>
         <v>104004</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="12">
         <v>4</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D8" s="1">
         <v>1026302</v>
       </c>
-      <c r="E8" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" s="11">
+      <c r="E8" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="12">
         <v>10</v>
       </c>
-      <c r="G8" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" s="11">
+      <c r="G8" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="12">
         <v>4</v>
       </c>
-      <c r="I8" s="10">
+      <c r="I8" s="11">
         <v>100103</v>
       </c>
-      <c r="J8" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="J8" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="K8" s="14">
+        <v>2026301</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="1:11">
       <c r="A9" s="6">
         <f t="shared" si="0"/>
         <v>105005</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="12">
         <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D9" s="1">
         <v>1026401</v>
       </c>
-      <c r="E9" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" s="11">
+      <c r="E9" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="12">
         <v>10</v>
       </c>
-      <c r="G9" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" s="11">
+      <c r="G9" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="12">
         <v>5</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="11">
         <v>100103</v>
       </c>
-      <c r="J9" s="13" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+      <c r="J9" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="K9" s="14">
+        <v>2026401</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="1:11">
       <c r="A10" s="6">
         <f t="shared" si="0"/>
         <v>201006</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="12">
         <v>6</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D10" s="1">
         <v>1027001</v>
       </c>
-      <c r="E10" s="12" t="s">
-        <v>36</v>
+      <c r="E10" s="13" t="s">
+        <v>38</v>
       </c>
       <c r="F10" s="6">
         <v>20</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H10" s="13">
+        <v>39</v>
+      </c>
+      <c r="H10" s="15">
         <v>1</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="11">
         <v>200102</v>
       </c>
-      <c r="J10" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+      <c r="J10" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" s="14">
+        <v>2027001</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="1:11">
       <c r="A11" s="6">
         <f t="shared" si="0"/>
         <v>202007</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="12">
         <v>7</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D11" s="1">
         <v>1027101</v>
       </c>
-      <c r="E11" s="12" t="s">
-        <v>39</v>
+      <c r="E11" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="F11" s="6">
         <v>20</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H11" s="13">
+        <v>39</v>
+      </c>
+      <c r="H11" s="15">
         <v>2</v>
       </c>
-      <c r="I11" s="10">
+      <c r="I11" s="11">
         <v>200102</v>
       </c>
-      <c r="J11" s="11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="J11" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="K11" s="14">
+        <v>2027101</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" spans="1:11">
       <c r="A12" s="6">
         <f t="shared" si="0"/>
         <v>203008</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="12">
         <v>8</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D12" s="1">
         <v>1027201</v>
       </c>
-      <c r="E12" s="12" t="s">
-        <v>41</v>
+      <c r="E12" s="13" t="s">
+        <v>43</v>
       </c>
       <c r="F12" s="6">
         <v>20</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H12" s="13">
+        <v>39</v>
+      </c>
+      <c r="H12" s="15">
         <v>3</v>
       </c>
-      <c r="I12" s="10">
+      <c r="I12" s="11">
         <v>200102</v>
       </c>
-      <c r="J12" s="11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+      <c r="J12" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="K12" s="14">
+        <v>2027201</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="1:11">
       <c r="A13" s="6">
         <f t="shared" si="0"/>
         <v>204009</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="12">
         <v>9</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D13" s="1">
         <v>1027301</v>
       </c>
-      <c r="E13" s="12" t="s">
-        <v>43</v>
+      <c r="E13" s="13" t="s">
+        <v>45</v>
       </c>
       <c r="F13" s="6">
         <v>20</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H13" s="13">
+        <v>39</v>
+      </c>
+      <c r="H13" s="15">
         <v>4</v>
       </c>
-      <c r="I13" s="10">
+      <c r="I13" s="11">
         <v>200102</v>
       </c>
-      <c r="J13" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+      <c r="J13" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="K13" s="14">
+        <v>2027301</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" spans="1:11">
       <c r="A14" s="6">
         <f t="shared" si="0"/>
         <v>205010</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="12">
         <v>10</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D14" s="1">
         <v>1027401</v>
       </c>
-      <c r="E14" s="12" t="s">
-        <v>45</v>
+      <c r="E14" s="13" t="s">
+        <v>47</v>
       </c>
       <c r="F14" s="6">
         <v>20</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H14" s="13">
+        <v>39</v>
+      </c>
+      <c r="H14" s="15">
         <v>5</v>
       </c>
-      <c r="I14" s="10">
+      <c r="I14" s="11">
         <v>200102</v>
       </c>
-      <c r="J14" s="13" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+      <c r="J14" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="K14" s="14">
+        <v>2027401</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" spans="1:11">
       <c r="A15" s="6">
         <f t="shared" si="0"/>
         <v>301011</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="12">
         <v>11</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D15" s="1">
         <v>1028001</v>
       </c>
-      <c r="E15" s="12" t="s">
-        <v>47</v>
+      <c r="E15" s="13" t="s">
+        <v>49</v>
       </c>
       <c r="F15" s="6">
         <v>30</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H15" s="6">
         <v>1</v>
       </c>
-      <c r="I15" s="10">
+      <c r="I15" s="11">
         <v>300103</v>
       </c>
-      <c r="J15" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+      <c r="J15" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="K15" s="14">
+        <v>2028001</v>
+      </c>
+    </row>
+    <row r="16" ht="16.5" spans="1:11">
       <c r="A16" s="6">
         <f t="shared" si="0"/>
         <v>302012</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="12">
         <v>12</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D16" s="1">
         <v>1028101</v>
       </c>
-      <c r="E16" s="12" t="s">
-        <v>50</v>
+      <c r="E16" s="13" t="s">
+        <v>52</v>
       </c>
       <c r="F16" s="6">
         <v>30</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H16" s="6">
         <v>2</v>
       </c>
-      <c r="I16" s="10">
+      <c r="I16" s="11">
         <v>300103</v>
       </c>
-      <c r="J16" s="11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+      <c r="J16" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="K16" s="14">
+        <v>2028101</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" spans="1:11">
       <c r="A17" s="6">
         <f t="shared" si="0"/>
         <v>303013</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="12">
         <v>13</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D17" s="1">
         <v>1028201</v>
       </c>
-      <c r="E17" s="12" t="s">
-        <v>52</v>
+      <c r="E17" s="13" t="s">
+        <v>54</v>
       </c>
       <c r="F17" s="6">
         <v>30</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H17" s="6">
         <v>3</v>
       </c>
-      <c r="I17" s="10">
+      <c r="I17" s="11">
         <v>300103</v>
       </c>
-      <c r="J17" s="11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+      <c r="J17" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="K17" s="14">
+        <v>2028201</v>
+      </c>
+    </row>
+    <row r="18" ht="16.5" spans="1:11">
       <c r="A18" s="6">
         <f t="shared" si="0"/>
         <v>304014</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="12">
         <v>14</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D18" s="1">
         <v>1028301</v>
       </c>
-      <c r="E18" s="12" t="s">
-        <v>54</v>
+      <c r="E18" s="13" t="s">
+        <v>56</v>
       </c>
       <c r="F18" s="6">
         <v>30</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H18" s="6">
         <v>4</v>
       </c>
-      <c r="I18" s="10">
+      <c r="I18" s="11">
         <v>300103</v>
       </c>
-      <c r="J18" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+      <c r="J18" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="K18" s="14">
+        <v>2028301</v>
+      </c>
+    </row>
+    <row r="19" ht="16.5" spans="1:11">
       <c r="A19" s="6">
         <f t="shared" si="0"/>
         <v>305015</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="12">
         <v>15</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D19" s="1">
         <v>1028401</v>
       </c>
-      <c r="E19" s="12" t="s">
-        <v>56</v>
+      <c r="E19" s="13" t="s">
+        <v>58</v>
       </c>
       <c r="F19" s="6">
         <v>30</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H19" s="6">
         <v>5</v>
       </c>
-      <c r="I19" s="10">
+      <c r="I19" s="11">
         <v>300103</v>
       </c>
-      <c r="J19" s="13" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+      <c r="J19" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="K19" s="14">
+        <v>2028401</v>
+      </c>
+    </row>
+    <row r="20" ht="16.5" spans="1:11">
       <c r="A20" s="6">
         <f t="shared" ref="A20:A34" si="1">F20*10000+H20*1000+B20</f>
         <v>101016</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="12">
         <v>16</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D20" s="1">
         <v>1026002</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F20" s="11">
+        <v>60</v>
+      </c>
+      <c r="F20" s="12">
         <v>10</v>
       </c>
-      <c r="G20" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="H20" s="11">
+      <c r="G20" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="12">
         <v>1</v>
       </c>
-      <c r="I20" s="10">
+      <c r="I20" s="11">
         <v>100103</v>
       </c>
-      <c r="J20" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+      <c r="J20" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="K20" s="14">
+        <v>2026002</v>
+      </c>
+    </row>
+    <row r="21" ht="16.5" spans="1:11">
       <c r="A21" s="6">
         <f t="shared" si="1"/>
         <v>102017</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="12">
         <v>17</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D21" s="1">
         <v>1026102</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F21" s="11">
+        <v>62</v>
+      </c>
+      <c r="F21" s="12">
         <v>10</v>
       </c>
-      <c r="G21" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="H21" s="11">
+      <c r="G21" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="12">
         <v>2</v>
       </c>
-      <c r="I21" s="10">
+      <c r="I21" s="11">
         <v>100103</v>
       </c>
-      <c r="J21" s="11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
+      <c r="J21" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="K21" s="14">
+        <v>2026102</v>
+      </c>
+    </row>
+    <row r="22" ht="16.5" spans="1:11">
       <c r="A22" s="6">
         <f t="shared" si="1"/>
         <v>103018</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="12">
         <v>18</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D22" s="1">
         <v>1026202</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F22" s="11">
+        <v>64</v>
+      </c>
+      <c r="F22" s="12">
         <v>10</v>
       </c>
-      <c r="G22" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="H22" s="11">
+      <c r="G22" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="12">
         <v>3</v>
       </c>
-      <c r="I22" s="10">
+      <c r="I22" s="11">
         <v>100103</v>
       </c>
-      <c r="J22" s="11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+      <c r="J22" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="K22" s="14">
+        <v>2026202</v>
+      </c>
+    </row>
+    <row r="23" ht="16.5" spans="1:11">
       <c r="A23" s="6">
         <f t="shared" si="1"/>
         <v>104019</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="12">
         <v>19</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D23" s="1">
         <v>1026302</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F23" s="11">
+        <v>66</v>
+      </c>
+      <c r="F23" s="12">
         <v>10</v>
       </c>
-      <c r="G23" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="H23" s="11">
+      <c r="G23" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" s="12">
         <v>4</v>
       </c>
-      <c r="I23" s="10">
+      <c r="I23" s="11">
         <v>100103</v>
       </c>
-      <c r="J23" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
+      <c r="J23" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="K23" s="14">
+        <v>2026302</v>
+      </c>
+    </row>
+    <row r="24" ht="16.5" spans="1:11">
       <c r="A24" s="6">
         <f t="shared" si="1"/>
         <v>105020</v>
       </c>
-      <c r="B24" s="11">
+      <c r="B24" s="12">
         <v>20</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D24" s="1">
         <v>1026402</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F24" s="11">
+        <v>68</v>
+      </c>
+      <c r="F24" s="12">
         <v>10</v>
       </c>
-      <c r="G24" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="H24" s="11">
+      <c r="G24" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H24" s="12">
         <v>5</v>
       </c>
-      <c r="I24" s="10">
+      <c r="I24" s="11">
         <v>100103</v>
       </c>
-      <c r="J24" s="13" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
+      <c r="J24" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="K24" s="14">
+        <v>2026402</v>
+      </c>
+    </row>
+    <row r="25" ht="16.5" spans="1:11">
       <c r="A25" s="6">
         <f t="shared" si="1"/>
         <v>201021</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="12">
         <v>21</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D25" s="1">
         <v>1027002</v>
       </c>
-      <c r="E25" s="14" t="s">
-        <v>68</v>
+      <c r="E25" s="16" t="s">
+        <v>70</v>
       </c>
       <c r="F25" s="6">
         <v>20</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H25" s="13">
+        <v>39</v>
+      </c>
+      <c r="H25" s="15">
         <v>1</v>
       </c>
-      <c r="I25" s="10">
+      <c r="I25" s="11">
         <v>200102</v>
       </c>
-      <c r="J25" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
+      <c r="J25" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="K25" s="14">
+        <v>2027002</v>
+      </c>
+    </row>
+    <row r="26" ht="16.5" spans="1:11">
       <c r="A26" s="6">
         <f t="shared" si="1"/>
         <v>202022</v>
       </c>
-      <c r="B26" s="11">
+      <c r="B26" s="12">
         <v>22</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D26" s="1">
         <v>1027102</v>
       </c>
-      <c r="E26" s="12" t="s">
-        <v>70</v>
+      <c r="E26" s="13" t="s">
+        <v>72</v>
       </c>
       <c r="F26" s="6">
         <v>20</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H26" s="13">
+        <v>39</v>
+      </c>
+      <c r="H26" s="15">
         <v>2</v>
       </c>
-      <c r="I26" s="10">
+      <c r="I26" s="11">
         <v>200102</v>
       </c>
-      <c r="J26" s="11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
+      <c r="J26" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="K26" s="14">
+        <v>2027102</v>
+      </c>
+    </row>
+    <row r="27" ht="16.5" spans="1:11">
       <c r="A27" s="6">
         <f t="shared" si="1"/>
         <v>203023</v>
       </c>
-      <c r="B27" s="11">
+      <c r="B27" s="12">
         <v>23</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D27" s="1">
         <v>1027202</v>
       </c>
-      <c r="E27" s="12" t="s">
-        <v>72</v>
+      <c r="E27" s="13" t="s">
+        <v>74</v>
       </c>
       <c r="F27" s="6">
         <v>20</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H27" s="13">
+        <v>39</v>
+      </c>
+      <c r="H27" s="15">
         <v>3</v>
       </c>
-      <c r="I27" s="10">
+      <c r="I27" s="11">
         <v>200102</v>
       </c>
-      <c r="J27" s="11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
+      <c r="J27" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="K27" s="14">
+        <v>2027202</v>
+      </c>
+    </row>
+    <row r="28" ht="16.5" spans="1:11">
       <c r="A28" s="6">
         <f t="shared" si="1"/>
         <v>204024</v>
       </c>
-      <c r="B28" s="11">
+      <c r="B28" s="12">
         <v>24</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D28" s="1">
         <v>1027302</v>
       </c>
-      <c r="E28" s="12" t="s">
-        <v>74</v>
+      <c r="E28" s="13" t="s">
+        <v>76</v>
       </c>
       <c r="F28" s="6">
         <v>20</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H28" s="13">
+        <v>39</v>
+      </c>
+      <c r="H28" s="15">
         <v>4</v>
       </c>
-      <c r="I28" s="10">
+      <c r="I28" s="11">
         <v>200102</v>
       </c>
-      <c r="J28" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
+      <c r="J28" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="K28" s="14">
+        <v>2027302</v>
+      </c>
+    </row>
+    <row r="29" ht="16.5" spans="1:11">
       <c r="A29" s="6">
         <f t="shared" si="1"/>
         <v>205025</v>
       </c>
-      <c r="B29" s="11">
+      <c r="B29" s="12">
         <v>25</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D29" s="1">
         <v>1027402</v>
       </c>
-      <c r="E29" s="12" t="s">
-        <v>76</v>
+      <c r="E29" s="13" t="s">
+        <v>78</v>
       </c>
       <c r="F29" s="6">
         <v>20</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H29" s="13">
+        <v>39</v>
+      </c>
+      <c r="H29" s="15">
         <v>5</v>
       </c>
-      <c r="I29" s="10">
+      <c r="I29" s="11">
         <v>200102</v>
       </c>
-      <c r="J29" s="13" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
+      <c r="J29" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="K29" s="14">
+        <v>2027402</v>
+      </c>
+    </row>
+    <row r="30" ht="16.5" spans="1:11">
       <c r="A30" s="6">
         <f t="shared" si="1"/>
         <v>301026</v>
       </c>
-      <c r="B30" s="11">
+      <c r="B30" s="12">
         <v>26</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D30" s="1">
         <v>1028002</v>
       </c>
-      <c r="E30" s="12" t="s">
-        <v>78</v>
+      <c r="E30" s="13" t="s">
+        <v>80</v>
       </c>
       <c r="F30" s="6">
         <v>30</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H30" s="6">
         <v>1</v>
       </c>
-      <c r="I30" s="10">
+      <c r="I30" s="11">
         <v>300103</v>
       </c>
-      <c r="J30" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
+      <c r="J30" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="K30" s="14">
+        <v>2028002</v>
+      </c>
+    </row>
+    <row r="31" ht="16.5" spans="1:11">
       <c r="A31" s="6">
         <f t="shared" si="1"/>
         <v>302027</v>
       </c>
-      <c r="B31" s="11">
+      <c r="B31" s="12">
         <v>27</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D31" s="1">
         <v>1028102</v>
       </c>
-      <c r="E31" s="12" t="s">
-        <v>80</v>
+      <c r="E31" s="13" t="s">
+        <v>82</v>
       </c>
       <c r="F31" s="6">
         <v>30</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H31" s="6">
         <v>2</v>
       </c>
-      <c r="I31" s="10">
+      <c r="I31" s="11">
         <v>300103</v>
       </c>
-      <c r="J31" s="11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
+      <c r="J31" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="K31" s="14">
+        <v>2028102</v>
+      </c>
+    </row>
+    <row r="32" ht="16.5" spans="1:11">
       <c r="A32" s="6">
         <f t="shared" si="1"/>
         <v>303028</v>
       </c>
-      <c r="B32" s="11">
+      <c r="B32" s="12">
         <v>28</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D32" s="1">
         <v>1028202</v>
       </c>
-      <c r="E32" s="12" t="s">
-        <v>82</v>
+      <c r="E32" s="13" t="s">
+        <v>84</v>
       </c>
       <c r="F32" s="6">
         <v>30</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H32" s="6">
         <v>3</v>
       </c>
-      <c r="I32" s="10">
+      <c r="I32" s="11">
         <v>300103</v>
       </c>
-      <c r="J32" s="11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10">
+      <c r="J32" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="K32" s="14">
+        <v>2028202</v>
+      </c>
+    </row>
+    <row r="33" ht="16.5" spans="1:11">
       <c r="A33" s="6">
         <f t="shared" si="1"/>
         <v>304029</v>
       </c>
-      <c r="B33" s="11">
+      <c r="B33" s="12">
         <v>29</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D33" s="1">
         <v>1028302</v>
       </c>
-      <c r="E33" s="12" t="s">
-        <v>84</v>
+      <c r="E33" s="13" t="s">
+        <v>86</v>
       </c>
       <c r="F33" s="6">
         <v>30</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H33" s="6">
         <v>4</v>
       </c>
-      <c r="I33" s="10">
+      <c r="I33" s="11">
         <v>300103</v>
       </c>
-      <c r="J33" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10">
+      <c r="J33" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="K33" s="14">
+        <v>2028302</v>
+      </c>
+    </row>
+    <row r="34" ht="16.5" spans="1:11">
       <c r="A34" s="6">
         <f t="shared" si="1"/>
         <v>305030</v>
       </c>
-      <c r="B34" s="11">
+      <c r="B34" s="12">
         <v>30</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D34" s="1">
         <v>1028402</v>
       </c>
-      <c r="E34" s="12" t="s">
-        <v>86</v>
+      <c r="E34" s="13" t="s">
+        <v>88</v>
       </c>
       <c r="F34" s="6">
         <v>30</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H34" s="6">
         <v>5</v>
       </c>
-      <c r="I34" s="10">
+      <c r="I34" s="11">
         <v>300103</v>
       </c>
-      <c r="J34" s="13" t="s">
-        <v>34</v>
+      <c r="J34" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="K34" s="14">
+        <v>2028402</v>
       </c>
     </row>
   </sheetData>
@@ -2812,13 +2930,13 @@
   <sheetData>
     <row r="11" spans="4:8">
       <c r="D11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="4:8">

--- a/hall/resources/sample/EmployeeProfile.xlsx
+++ b/hall/resources/sample/EmployeeProfile.xlsx
@@ -1955,7 +1955,7 @@
         <v>31</v>
       </c>
       <c r="D8" s="1">
-        <v>1026302</v>
+        <v>1026301</v>
       </c>
       <c r="E8" s="13" t="s">
         <v>32</v>
